--- a/assets/risk/Risk & Return Review Solutions.xlsx
+++ b/assets/risk/Risk & Return Review Solutions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox\Courses\Teaching\Financial Analytics\Course\3 - Risk &amp; Return\4 - Exercises\1 - Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F2CDCC6-1719-49CA-98FF-F6970ED582DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC043F5-A812-4F8A-AC57-A139635523EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10876" xr2:uid="{6EE16BD3-821C-4EF1-8275-74C7E8006C6F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10876" activeTab="3" xr2:uid="{6EE16BD3-821C-4EF1-8275-74C7E8006C6F}"/>
   </bookViews>
   <sheets>
     <sheet name="Problems 1-4" sheetId="1" r:id="rId1"/>
@@ -5863,8 +5863,8 @@
         <v>3.3489999999999999E-2</v>
       </c>
       <c r="E2" s="8">
-        <f>SUMPRODUCT(B2:D2,$I$6:$K$6)</f>
-        <v>5.7600199999999997E-2</v>
+        <f>SUMPRODUCT(B2:D2,$H$6:$J$6)</f>
+        <v>3.0808200104208785E-2</v>
       </c>
       <c r="G2" t="s">
         <v>4</v>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="K2" s="8">
         <f t="shared" si="0"/>
-        <v>2.7915856666666673E-2</v>
+        <v>1.9356590239484581E-2</v>
       </c>
       <c r="L2" s="17" t="str">
         <f ca="1">_xlfn.FORMULATEXT(K2)</f>
@@ -5904,8 +5904,8 @@
         <v>-8.3927000000000002E-2</v>
       </c>
       <c r="E3" s="8">
-        <f t="shared" ref="E3:E66" si="1">SUMPRODUCT(B3:D3,$I$6:$K$6)</f>
-        <v>-0.1125232</v>
+        <f t="shared" ref="E3:E66" si="1">SUMPRODUCT(B3:D3,$H$6:$J$6)</f>
+        <v>-4.5381600129779182E-2</v>
       </c>
       <c r="G3" t="s">
         <v>3</v>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="K3" s="8">
         <f t="shared" si="2"/>
-        <v>0.12118751044605655</v>
+        <v>7.4822897182153195E-2</v>
       </c>
       <c r="L3" s="17" t="str">
         <f t="shared" ref="L3:L5" ca="1" si="3">_xlfn.FORMULATEXT(K3)</f>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E4" s="8">
         <f t="shared" si="1"/>
-        <v>5.2083999999999998E-2</v>
+        <v>6.0604000974506113E-2</v>
       </c>
       <c r="G4" t="s">
         <v>8</v>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="K4" s="8">
         <f t="shared" si="4"/>
-        <v>2.2915856666666672E-2</v>
+        <v>1.435659023948458E-2</v>
       </c>
       <c r="L4" s="17" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="E5" s="8">
         <f t="shared" si="1"/>
-        <v>0.12453880000000001</v>
+        <v>6.5120400736693521E-2</v>
       </c>
       <c r="G5" t="s">
         <v>6</v>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="K5" s="20">
         <f t="shared" si="5"/>
-        <v>0.18909421096546963</v>
+        <v>0.19187428955783503</v>
       </c>
       <c r="L5" s="17" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -6028,23 +6028,23 @@
       </c>
       <c r="E6" s="8">
         <f t="shared" si="1"/>
-        <v>0.16825220000000002</v>
+        <v>0.14553780212926662</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
       </c>
       <c r="H6" s="8">
+        <v>0.60000000993410718</v>
+      </c>
+      <c r="I6" s="8">
         <v>0.2</v>
-      </c>
-      <c r="I6" s="8">
-        <v>0.6</v>
       </c>
       <c r="J6" s="8">
         <v>0.2</v>
       </c>
       <c r="K6" s="8">
         <f>SUM(H6:J6)</f>
-        <v>1</v>
+        <v>1.0000000099341071</v>
       </c>
       <c r="L6" s="3"/>
     </row>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="E7" s="8">
         <f t="shared" si="1"/>
-        <v>-2.5595E-2</v>
+        <v>6.2098000695884215E-3</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="E8" s="8">
         <f t="shared" si="1"/>
-        <v>2.6640199999999992E-2</v>
+        <v>3.9670600791211895E-2</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="E9" s="8">
         <f t="shared" si="1"/>
-        <v>2.7141000000000002E-2</v>
+        <v>3.1556200506659332E-2</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.45">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="E10" s="8">
         <f t="shared" si="1"/>
-        <v>0.11054940000000001</v>
+        <v>9.0222201075337294E-2</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.45">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="E11" s="8">
         <f t="shared" si="1"/>
-        <v>0.44137559999999998</v>
+        <v>0.24178280236134722</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="E12" s="8">
         <f t="shared" si="1"/>
-        <v>-0.1125934</v>
+        <v>-4.5220600404268493E-2</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="E13" s="8">
         <f t="shared" si="1"/>
-        <v>0.1113082</v>
+        <v>6.3689000864644824E-2</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.45">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="E14" s="8">
         <f t="shared" si="1"/>
-        <v>-0.3110388</v>
+        <v>-0.24362280314553569</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.45">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="E15" s="8">
         <f t="shared" si="1"/>
-        <v>-0.2411102</v>
+        <v>-0.11129180075885652</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.45">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="E16" s="8">
         <f t="shared" si="1"/>
-        <v>0.11904019999999998</v>
+        <v>8.4331401468419984E-2</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="E17" s="8">
         <f t="shared" si="1"/>
-        <v>0.1930124</v>
+        <v>0.18906600210796787</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E18" s="8">
         <f t="shared" si="1"/>
-        <v>5.1901600000000006E-2</v>
+        <v>5.4426400845213711E-2</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="E19" s="8">
         <f t="shared" si="1"/>
-        <v>-0.11661580000000001</v>
+        <v>-9.3734201121570646E-2</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="E20" s="8">
         <f t="shared" si="1"/>
-        <v>-0.11550060000000001</v>
+        <v>-6.3447000503708911E-2</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="E21" s="8">
         <f t="shared" si="1"/>
-        <v>0.1008404</v>
+        <v>4.8585200661234042E-2</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="E22" s="8">
         <f t="shared" si="1"/>
-        <v>-0.24681840000000002</v>
+        <v>-0.22922960327386449</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="E23" s="8">
         <f t="shared" si="1"/>
-        <v>-0.21595320000000001</v>
+        <v>-8.5267600530531007E-2</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="E24" s="8">
         <f t="shared" si="1"/>
-        <v>-0.20882959999999998</v>
+        <v>-0.13789360137761231</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="E25" s="8">
         <f t="shared" si="1"/>
-        <v>-7.5941399999999992E-2</v>
+        <v>-4.5080600784695127E-2</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="E26" s="8">
         <f t="shared" si="1"/>
-        <v>-6.6692200000000007E-2</v>
+        <v>2.9603800556359677E-2</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="E27" s="8">
         <f t="shared" si="1"/>
-        <v>-5.3730800000000002E-2</v>
+        <v>-1.5368400090380509E-2</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="E28" s="8">
         <f t="shared" si="1"/>
-        <v>0.24963419999999997</v>
+        <v>0.13966540175857539</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E29" s="8">
         <f t="shared" si="1"/>
-        <v>0.2486226</v>
+        <v>0.16631460195714826</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="E30" s="8">
         <f t="shared" si="1"/>
-        <v>9.5837999999999993E-2</v>
+        <v>6.5828400787903835E-2</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.45">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="E31" s="8">
         <f t="shared" si="1"/>
-        <v>0.16920199999999999</v>
+        <v>5.891000048423805E-2</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="E32" s="8">
         <f t="shared" si="1"/>
-        <v>8.7959599999999999E-2</v>
+        <v>9.6373201461903216E-2</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="E33" s="8">
         <f t="shared" si="1"/>
-        <v>7.9676399999999994E-2</v>
+        <v>3.6819600293056157E-2</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="E34" s="8">
         <f t="shared" si="1"/>
-        <v>0.11935280000000001</v>
+        <v>8.4626401012245792E-2</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="E35" s="8">
         <f t="shared" si="1"/>
-        <v>0.1045888</v>
+        <v>4.206960016883015E-2</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="E36" s="8">
         <f t="shared" si="1"/>
-        <v>0.1190792</v>
+        <v>6.6861600601321458E-2</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="E37" s="8">
         <f t="shared" si="1"/>
-        <v>8.1548399999999993E-2</v>
+        <v>5.2442800537772963E-2</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.45">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="E38" s="8">
         <f t="shared" si="1"/>
-        <v>-0.1576584</v>
+        <v>-9.7291200880072495E-2</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="E39" s="8">
         <f t="shared" si="1"/>
-        <v>6.0042399999999989E-2</v>
+        <v>4.2441600649491922E-2</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="E40" s="8">
         <f t="shared" si="1"/>
-        <v>0.1259276</v>
+        <v>0.10869720147491689</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.45">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="E41" s="8">
         <f t="shared" si="1"/>
-        <v>9.4598799999999997E-2</v>
+        <v>6.0522801102894506E-2</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="E42" s="8">
         <f t="shared" si="1"/>
-        <v>-0.17572860000000001</v>
+        <v>-5.507980016018748E-2</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="E43" s="8">
         <f t="shared" si="1"/>
-        <v>-0.1373896</v>
+        <v>-5.0877600206897647E-2</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="E44" s="8">
         <f t="shared" si="1"/>
-        <v>0.15326519999999999</v>
+        <v>5.5916400225911538E-2</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="E45" s="8">
         <f t="shared" si="1"/>
-        <v>-0.13318940000000001</v>
+        <v>-6.4534200546425571E-2</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="E46" s="8">
         <f t="shared" si="1"/>
-        <v>0.17768500000000001</v>
+        <v>0.14273940166113175</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="E47" s="8">
         <f t="shared" si="1"/>
-        <v>0.15868499999999999</v>
+        <v>8.7635400603228789E-2</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="E48" s="8">
         <f t="shared" si="1"/>
-        <v>-4.5408400000000002E-2</v>
+        <v>-7.9811996643265205E-3</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="E49" s="8">
         <f t="shared" si="1"/>
-        <v>0.14078979999999999</v>
+        <v>5.6775400364283704E-2</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="E50" s="8">
         <f t="shared" si="1"/>
-        <v>2.6698999999999994E-2</v>
+        <v>3.2001400516166269E-2</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="E51" s="8">
         <f t="shared" si="1"/>
-        <v>-6.6229999999999969E-3</v>
+        <v>2.1799400406652677E-2</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="E52" s="8">
         <f t="shared" si="1"/>
-        <v>-6.1445399999999997E-2</v>
+        <v>-2.5628600132262702E-2</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="E53" s="8">
         <f t="shared" si="1"/>
-        <v>9.1267999999999991E-3</v>
+        <v>-7.5723999537467982E-3</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="E54" s="8">
         <f t="shared" si="1"/>
-        <v>-3.8419399999999999E-2</v>
+        <v>-1.5271400065257151E-2</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="E55" s="8">
         <f t="shared" si="1"/>
-        <v>1.0048800000000004E-2</v>
+        <v>-2.1618400347296382E-2</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="E56" s="8">
         <f t="shared" si="1"/>
-        <v>0.19025060000000002</v>
+        <v>0.14717380162209071</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="E57" s="8">
         <f t="shared" si="1"/>
-        <v>-5.2821599999999996E-2</v>
+        <v>-3.4135200143736597E-2</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="E58" s="8">
         <f t="shared" si="1"/>
-        <v>-7.9341599999999998E-2</v>
+        <v>-2.7912800090608994E-2</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="E59" s="8">
         <f t="shared" si="1"/>
-        <v>0.1369554</v>
+        <v>8.1029000611176072E-2</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="E60" s="8">
         <f t="shared" si="1"/>
-        <v>-6.3110800000000009E-2</v>
+        <v>-3.75756005541543E-2</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="E61" s="8">
         <f t="shared" si="1"/>
-        <v>6.6167200000000009E-2</v>
+        <v>5.4283200592619166E-2</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="E62" s="8">
         <f t="shared" si="1"/>
-        <v>0.193414</v>
+        <v>8.3398801262734301E-2</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="E63" s="8">
         <f t="shared" si="1"/>
-        <v>0.20774779999999998</v>
+        <v>0.14245820187070168</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.45">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="E64" s="8">
         <f t="shared" si="1"/>
-        <v>8.6833600000000011E-2</v>
+        <v>7.3852801045902555E-2</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.45">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="E65" s="8">
         <f t="shared" si="1"/>
-        <v>-3.4372199999999999E-2</v>
+        <v>-2.8419400257978827E-2</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="E66" s="8">
         <f t="shared" si="1"/>
-        <v>-9.6346799999999996E-2</v>
+        <v>-3.0752400106314814E-2</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.45">
@@ -7142,8 +7142,8 @@
         <v>4.7961999999999998E-2</v>
       </c>
       <c r="E67" s="8">
-        <f t="shared" ref="E67:E121" si="6">SUMPRODUCT(B67:D67,$I$6:$K$6)</f>
-        <v>5.4201799999999994E-2</v>
+        <f t="shared" ref="E67:E121" si="6">SUMPRODUCT(B67:D67,$H$6:$J$6)</f>
+        <v>1.5832200107814866E-2</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="E68" s="8">
         <f t="shared" si="6"/>
-        <v>9.1193999999999997E-3</v>
+        <v>3.8409800455200663E-2</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.45">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="E69" s="8">
         <f t="shared" si="6"/>
-        <v>0.12518779999999999</v>
+        <v>8.3111000929226464E-2</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="E70" s="8">
         <f t="shared" si="6"/>
-        <v>-1.2448199999999996E-2</v>
+        <v>1.5066200027845306E-2</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="E71" s="8">
         <f t="shared" si="6"/>
-        <v>-0.12522839999999999</v>
+        <v>-9.2432401068979458E-2</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="E72" s="8">
         <f t="shared" si="6"/>
-        <v>-6.1524799999999998E-2</v>
+        <v>-1.4012800123312071E-2</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="E73" s="8">
         <f t="shared" si="6"/>
-        <v>-4.8304600000000003E-2</v>
+        <v>-5.1151000901401018E-2</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="E74" s="8">
         <f t="shared" si="6"/>
-        <v>-4.5080600000000005E-2</v>
+        <v>-6.725420143144524E-2</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="E75" s="8">
         <f t="shared" si="6"/>
-        <v>1.8104000000000002E-2</v>
+        <v>1.2007997504949654E-3</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="E76" s="8">
         <f t="shared" si="6"/>
-        <v>2.89196E-2</v>
+        <v>5.7540000283618758E-3</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="E77" s="8">
         <f t="shared" si="6"/>
-        <v>0.16495360000000001</v>
+        <v>3.9241600002692147E-2</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="E78" s="8">
         <f t="shared" si="6"/>
-        <v>8.6201200000000006E-2</v>
+        <v>3.7138000224471085E-2</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="E79" s="8">
         <f t="shared" si="6"/>
-        <v>-7.9052799999999993E-2</v>
+        <v>-7.0915201175234685E-2</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="E80" s="8">
         <f t="shared" si="6"/>
-        <v>8.1075999999999926E-3</v>
+        <v>7.0750801402944277E-2</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="E81" s="8">
         <f t="shared" si="6"/>
-        <v>9.7049399999999994E-2</v>
+        <v>5.2074200828395263E-2</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.45">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="E82" s="8">
         <f t="shared" si="6"/>
-        <v>-9.6307999999999984E-3</v>
+        <v>-6.7564002133945547E-3</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="E83" s="8">
         <f t="shared" si="6"/>
-        <v>0.157</v>
+        <v>0.10591840095750886</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="E84" s="8">
         <f t="shared" si="6"/>
-        <v>0.1323086</v>
+        <v>6.4408600692139051E-2</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="E85" s="8">
         <f t="shared" si="6"/>
-        <v>-2.0051999999999987E-3</v>
+        <v>1.3101200088433422E-2</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="E86" s="8">
         <f t="shared" si="6"/>
-        <v>-4.2370400000000003E-2</v>
+        <v>-5.156560106987354E-2</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="E87" s="8">
         <f t="shared" si="6"/>
-        <v>6.0079800000000003E-2</v>
+        <v>4.4223800569333623E-2</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="E88" s="8">
         <f t="shared" si="6"/>
-        <v>6.5288200000000005E-2</v>
+        <v>9.3234001982152419E-3</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="E89" s="8">
         <f t="shared" si="6"/>
-        <v>3.6915599999999993E-2</v>
+        <v>4.8430800987410511E-2</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.45">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="E90" s="8">
         <f t="shared" si="6"/>
-        <v>8.1021599999999999E-2</v>
+        <v>6.478400077777105E-2</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.45">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="E91" s="8">
         <f t="shared" si="6"/>
-        <v>3.9716399999999999E-2</v>
+        <v>2.4865200274797272E-2</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="E92" s="8">
         <f t="shared" si="6"/>
-        <v>5.0499200000000001E-2</v>
+        <v>2.2489600285416834E-2</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.45">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="E93" s="8">
         <f t="shared" si="6"/>
-        <v>0.106307</v>
+        <v>5.9041400765840191E-2</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.45">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="E94" s="8">
         <f t="shared" si="6"/>
-        <v>1.2305E-2</v>
+        <v>-4.0718001696050136E-3</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.45">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="E95" s="8">
         <f t="shared" si="6"/>
-        <v>4.8920400000000003E-2</v>
+        <v>3.8739600714858352E-2</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.45">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="E96" s="8">
         <f t="shared" si="6"/>
-        <v>8.1635799999999994E-2</v>
+        <v>6.1699801048604612E-2</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.45">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="E97" s="8">
         <f t="shared" si="6"/>
-        <v>-7.8289999999999998E-2</v>
+        <v>-5.5533200714172899E-2</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.45">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="E98" s="8">
         <f t="shared" si="6"/>
-        <v>-9.0796800000000011E-2</v>
+        <v>1.3401600610192601E-2</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.45">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="E99" s="8">
         <f t="shared" si="6"/>
-        <v>0.16267680000000001</v>
+        <v>8.822160099799034E-2</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.45">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="E100" s="8">
         <f t="shared" si="6"/>
-        <v>-9.4504199999999997E-2</v>
+        <v>-3.6214600311652807E-2</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.45">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="E101" s="8">
         <f t="shared" si="6"/>
-        <v>0.19774259999999999</v>
+        <v>4.0615400057478747E-2</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.45">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="E102" s="8">
         <f t="shared" si="6"/>
-        <v>-4.3917999999999978E-3</v>
+        <v>1.9785800448485207E-2</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.45">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="E103" s="8">
         <f t="shared" si="6"/>
-        <v>-8.2128000000000007E-2</v>
+        <v>-3.5862400370204439E-2</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.45">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="E104" s="8">
         <f t="shared" si="6"/>
-        <v>8.1525600000000004E-2</v>
+        <v>3.5319199673287081E-2</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.45">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="E105" s="8">
         <f t="shared" si="6"/>
-        <v>-0.10407059999999999</v>
+        <v>-5.4905800656813365E-2</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.45">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="E106" s="8">
         <f t="shared" si="6"/>
-        <v>9.9700000000000136E-4</v>
+        <v>-1.2606200216722482E-2</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.45">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="E107" s="8">
         <f t="shared" si="6"/>
-        <v>0.27040419999999998</v>
+        <v>0.11893540082859395</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.45">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="E108" s="8">
         <f t="shared" si="6"/>
-        <v>4.2815399999999997E-2</v>
+        <v>1.1356199943474931E-2</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.45">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="E109" s="8">
         <f t="shared" si="6"/>
-        <v>-4.1371199999999997E-2</v>
+        <v>-5.8004001095016765E-2</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.45">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="E110" s="8">
         <f t="shared" si="6"/>
-        <v>-5.6458000000000001E-2</v>
+        <v>-5.0834000747462089E-2</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.45">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="E111" s="8">
         <f t="shared" si="6"/>
-        <v>-8.2279600000000008E-2</v>
+        <v>-2.6370800013262037E-2</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.45">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="E112" s="8">
         <f t="shared" si="6"/>
-        <v>0.17455959999999998</v>
+        <v>0.1061636012637277</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.45">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="E113" s="8">
         <f t="shared" si="6"/>
-        <v>-0.19542559999999998</v>
+        <v>-0.11778640138999022</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.45">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="E114" s="8">
         <f t="shared" si="6"/>
-        <v>0.12437819999999999</v>
+        <v>6.8392600708977361E-2</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.45">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="E115" s="8">
         <f t="shared" si="6"/>
-        <v>-7.2227800000000009E-2</v>
+        <v>-4.4605400423789007E-2</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.45">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="E116" s="8">
         <f t="shared" si="6"/>
-        <v>0.1866804</v>
+        <v>0.1005364008946955</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.45">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="E117" s="8">
         <f t="shared" si="6"/>
-        <v>3.39E-2</v>
+        <v>1.7809600234504536E-2</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.45">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="E118" s="8">
         <f t="shared" si="6"/>
-        <v>4.5336600000000005E-2</v>
+        <v>4.3387800650723764E-2</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.45">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="E119" s="8">
         <f t="shared" si="6"/>
-        <v>4.4331000000000002E-2</v>
+        <v>1.2108600043054422E-2</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.45">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="E120" s="8">
         <f t="shared" si="6"/>
-        <v>-9.1648000000000007E-3</v>
+        <v>-1.8911200214358163E-2</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.45">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="E121" s="8">
         <f t="shared" si="6"/>
-        <v>6.4242199999999999E-2</v>
+        <v>3.9283800476390109E-2</v>
       </c>
     </row>
   </sheetData>
